--- a/final_data/RNA_modifications_manifest.xlsx
+++ b/final_data/RNA_modifications_manifest.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38_Illumina.bed</t>
+          <t>polyA-RNA_hg38_SRS.bed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_Illumina.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_SRS.bigBed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38_ONT.bed</t>
+          <t>polyA-RNA_hg38_LRS.bed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ONT</t>
+          <t>LRS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_ONT.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_LRS.bigBed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tRNA_Illumina.bed</t>
+          <t>tRNA_SRS.bed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_Illumina.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_SRS.bigBed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rRNA_Illumina.bed</t>
+          <t>rRNA_SRS.bed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_Illumina.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_SRS.bigBed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rRNA_ONT.bed</t>
+          <t>rRNA_LRS.bed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ONT</t>
+          <t>LRS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_ONT.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_LRS.bigBed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/final_data/RNA_modifications_manifest.xlsx
+++ b/final_data/RNA_modifications_manifest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>This consensus file catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
+          <t>This track catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>This file includes predicted RNA modifications using ONT dorado modification-aware basecalling models. RNA modified sites were grouped into two tiers: i) tier 1 Reflects sites which show a significant modification level change between IVT and native RNA; ii) tier 2 reflects sites which did not have IVT with sufficient coverage, but showed a score &gt;0.9 derived from the equally weighted sum of min max normalized log2(coverage), modification level and model confidence ranks.</t>
+          <t>This track includes predicted RNA modifications using ONT dorado modification-aware basecalling models. RNA modified sites were grouped into two tiers: i) tier 1 Reflects sites which show a significant modification level change between IVT and native RNA; ii) tier 2 reflects sites which did not have IVT with sufficient coverage, but showed a score &gt;0.9 derived from the equally weighted sum of min max normalized log2(coverage), modification level and model confidence ranks.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -515,27 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tRNA_SRS.bed</t>
+          <t>polyA-RNA_hg38_consensus_tiered.bed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tRNA</t>
+          <t>polyA-RNA_hg38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>Tiered</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>This consensus file catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
+          <t>This concensus track represents RNA modification sites aggregated from sites detected by short-read sequencing (Illumina) and long-read sequencing (ONT) technologies. The sites are grouped into two confidence tiers: tier 1 reflects the strongest evidence from optimized cross-platform comparisons, and tier 2 comes from agreement between two or more raw datasets. Together they provide a ranked reference atlas of RNA modifications, with higher tiers representing sites supported by more independent lines of evidence.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_SRS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_consensus_tiered.bigBed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tRNA_MS.bed</t>
+          <t>tRNA_SRS.bed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This file catalogues modifications identified via oligonucleotide mass spectrometry across all submitted samples. Entries meet the following minimum quality thresholds: a false discovery rate (FDR) ≤ 5% for the detected oligonucleotide, a modification level ≥ 10%, and concordant detection across all samples covering the respective position.</t>
+          <t>This track catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_MS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_SRS.bigBed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -579,27 +579,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rRNA_SRS.bed</t>
+          <t>tRNA_MS.bed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rRNA</t>
+          <t>tRNA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>This consensus file catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
+          <t>This track catalogues modifications identified via oligonucleotide mass spectrometry across all submitted samples. Entries meet the following minimum quality thresholds: a false discovery rate (FDR) ≤ 5% for the detected oligonucleotide, a modification level ≥ 10%, and concordant detection across all samples covering the respective position.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_SRS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_MS.bigBed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,27 +611,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rRNA_LRS.bed</t>
+          <t>tRNA_consensus_tiered.bed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rRNA</t>
+          <t>tRNA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LRS</t>
+          <t>Tiered</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>This file includes predicted RNA modifications using ONT dorado modification-aware basecalling models. RNA modified sites were grouped into two tiers: i) tier 1 Reflects sites which show a significant modification level change between IVT and native RNA; ii) tier 2 reflects sites which did not have IVT with sufficient coverage, but showed a score &gt;0.9 derived from the equally weighted sum of min max normalized log2(coverage), modification level and model confidence ranks.</t>
+          <t>This concensus track represents RNA modification sites aggregated from sites detected by short-read sequencing (Illumina) and mass spectrometry technologies. The sites are grouped into two confidence tiers: tier 1 reflects the strongest evidence from optimized cross-platform comparisons, and tier 2 comes from agreement between two or more raw datasets. Together they provide a ranked reference atlas of RNA modifications, with higher tiers representing sites supported by more independent lines of evidence.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_LRS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/trna/tRNA_consensus_tiered.bigBed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,30 +643,126 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rRNA_SRS.bed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rRNA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>This track catalogues all RNA modification sites identified using the Illumina platform. It aggregates diverse modification types from multiple methods, retaining high-confidence sites supported by at least two replicates per method.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_SRS.bigBed</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rRNA_LRS.bed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rRNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LRS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>This track includes predicted RNA modifications using ONT dorado modification-aware basecalling models. RNA modified sites were grouped into two tiers: i) tier 1 Reflects sites which show a significant modification level change between IVT and native RNA; ii) tier 2 reflects sites which did not have IVT with sufficient coverage, but showed a score &gt;0.9 derived from the equally weighted sum of min max normalized log2(coverage), modification level and model confidence ranks.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_LRS.bigBed</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>rRNA_MS.bed</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>rRNA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>This file catalogues modifications identified via oligonucleotide mass spectrometry across all submitted samples. Entries meet the following minimum quality thresholds: a false discovery rate (FDR) ≤ 5% for the detected oligonucleotide, a modification level ≥ 10%, and concordant detection across all samples covering the respective position.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>This track catalogues modifications identified via oligonucleotide mass spectrometry across all submitted samples. Entries meet the following minimum quality thresholds: a false discovery rate (FDR) ≤ 5% for the detected oligonucleotide, a modification level ≥ 10%, and concordant detection across all samples covering the respective position.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_MS.bigBed</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rRNA_consensus_tiered.bed</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rRNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tiered</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This concensus track represents RNA modification sites aggregated from sites detected by short-read sequencing (Illumina), long-read sequencing (ONT), and mass spectrometry technologies. The sites are grouped into two confidence tiers: tier 1 reflects the strongest evidence from optimized cross-platform comparisons, and tier 2 comes from agreement between two or more raw datasets. Together they provide a ranked reference atlas of RNA modifications, with higher tiers representing sites supported by more independent lines of evidence.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/rrna/rRNA_consensus_tiered.bigBed</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>PLACEHOLDER_DOI</t>
         </is>

--- a/final_data/RNA_modifications_manifest.xlsx
+++ b/final_data/RNA_modifications_manifest.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38_SRS.bed</t>
+          <t>polyA_RNA_hg38_SRS.bed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38</t>
+          <t>polyA_RNA_hg38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_SRS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA_RNA_hg38_SRS.bigBed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38_LRS.bed</t>
+          <t>polyA_RNA_hg38_LRS.bed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38</t>
+          <t>polyA_RNA_hg38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_LRS.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA_RNA_hg38_LRS.bigBed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38_consensus_tiered.bed</t>
+          <t>polyA_RNA_hg38_consensus_tiered.bed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>polyA-RNA_hg38</t>
+          <t>polyA_RNA_hg38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA-RNA_hg38_consensus_tiered.bigBed</t>
+          <t>https://raw.githubusercontent.com/baihesun/RNome_UCSC_hub/main/ucsc_hub/hg38_polyA-RNA/polyA_RNA_hg38_consensus_tiered.bigBed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
